--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Expired'!$A$1:$AG$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Upcoming'!$A$1:$AG$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Calendar'!$A$1:$AG$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'History'!$A$1:$E$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'History'!$A$1:$E$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E196"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -819,7 +819,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09T19:44:38</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09T19:44:38</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09T19:44:38</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09T19:44:38</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09T19:44:38</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -954,135 +954,135 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:25</t>
+          <t>2026-07-09T19:44:38</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>87c39fd40a57</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>verification_timestamp</t>
+          <t>department</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:25</t>
+          <t>Department of Space (DOS)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:25</t>
+          <t>2026-07-09T19:44:38</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>b66db2d0d2ec</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>verification_timestamp</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:25</t>
+          <t>Department of Space (DOS)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:25</t>
+          <t>2026-07-09T19:44:38</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>02d9e5e0ad90</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>verification_timestamp</t>
+          <t>department</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>Department of Space (DOS)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:25</t>
+          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:25</t>
+          <t>2026-07-09T19:44:38</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0a30e8722b26</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>verification_timestamp</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>Department of Space (DOS)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:25</t>
+          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:25</t>
+          <t>2026-07-09T19:44:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26443cbd0d0b</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>verification_timestamp</t>
+          <t>verification_status</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>Application Closed</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:25</t>
+          <t>Verified with Official Website</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>fbea3ca3776a</t>
+          <t>87c39fd40a57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>54ce956af53b</t>
+          <t>b66db2d0d2ec</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>df468c72de0f</t>
+          <t>02d9e5e0ad90</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>e04acb52da48</t>
+          <t>0a30e8722b26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>e4c122dce080</t>
+          <t>26443cbd0d0b</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>b2f664f0544d</t>
+          <t>fbea3ca3776a</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6957d7d8c20a</t>
+          <t>54ce956af53b</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6bc3d38f7b5b</t>
+          <t>df468c72de0f</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7bb975daeff4</t>
+          <t>e04acb52da48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>c0eb547bae1c</t>
+          <t>e4c122dce080</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>965ad437043b</t>
+          <t>b2f664f0544d</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>a86501c2e700</t>
+          <t>6957d7d8c20a</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>646ab28ec176</t>
+          <t>6bc3d38f7b5b</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>516d962f09b7</t>
+          <t>7bb975daeff4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>03ddb8215a94</t>
+          <t>c0eb547bae1c</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6b52b5b11eff</t>
+          <t>965ad437043b</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>85865b3e20b9</t>
+          <t>a86501c2e700</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>cce3fa39da86</t>
+          <t>646ab28ec176</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>a2ca30a350bc</t>
+          <t>516d962f09b7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>bdb59e70824e</t>
+          <t>03ddb8215a94</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>964555e17606</t>
+          <t>6b52b5b11eff</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>b119f586189d</t>
+          <t>85865b3e20b9</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>9da8e5474470</t>
+          <t>cce3fa39da86</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>a526278063a8</t>
+          <t>a2ca30a350bc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>64ddfd6c77fa</t>
+          <t>bdb59e70824e</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>aac8b61baf33</t>
+          <t>964555e17606</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>bd78d582c083</t>
+          <t>b119f586189d</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>09be33473806</t>
+          <t>9da8e5474470</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>b002565b1c12</t>
+          <t>a526278063a8</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>05d054c7ae93</t>
+          <t>64ddfd6c77fa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>dd782eb47fcc</t>
+          <t>aac8b61baf33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7e0736826c66</t>
+          <t>bd78d582c083</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>b38d90158954</t>
+          <t>09be33473806</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6c8510c5d13d</t>
+          <t>b002565b1c12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2a55ae762d7f</t>
+          <t>05d054c7ae93</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>d8d82ac387aa</t>
+          <t>dd782eb47fcc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>e8a602cefe8a</t>
+          <t>7e0736826c66</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3e597427454a</t>
+          <t>b38d90158954</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>a0ff1af0d4a3</t>
+          <t>6c8510c5d13d</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6d91fcdbba27</t>
+          <t>2a55ae762d7f</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>38b1c543df1a</t>
+          <t>d8d82ac387aa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>72ea41d9bf79</t>
+          <t>e8a602cefe8a</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>51552f200f09</t>
+          <t>3e597427454a</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ec95bd2ff71c</t>
+          <t>a0ff1af0d4a3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>f14420c146b6</t>
+          <t>6d91fcdbba27</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ccac08fce58d</t>
+          <t>38b1c543df1a</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>df124ed2dfe8</t>
+          <t>72ea41d9bf79</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1f8689d713f5</t>
+          <t>51552f200f09</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4110c19d8a82</t>
+          <t>ec95bd2ff71c</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14e0b33e3461</t>
+          <t>f14420c146b6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>950b24b5dceb</t>
+          <t>ccac08fce58d</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ac346e8065ab</t>
+          <t>df124ed2dfe8</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>dce7ed17ece1</t>
+          <t>1f8689d713f5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>66103b82ca0e</t>
+          <t>4110c19d8a82</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2547,12 +2547,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>2026-07-09T19:43:25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7bd733e818b9</t>
+          <t>14e0b33e3461</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2562,24 +2562,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>2026-07-09T19:43:25</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>2026-07-09T19:43:25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>d3fa5ad79bf5</t>
+          <t>950b24b5dceb</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2589,24 +2589,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>2026-07-09T19:43:25</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>2026-07-09T19:43:25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3a36ceba0867</t>
+          <t>ac346e8065ab</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2616,24 +2616,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>2026-07-09T19:43:25</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>2026-07-09T19:43:25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>33e2483ac677</t>
+          <t>dce7ed17ece1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2643,24 +2643,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>2026-07-09T19:43:25</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>2026-07-09T19:43:25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ee0a2bf12529</t>
+          <t>66103b82ca0e</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>2026-07-09T19:43:25</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>717881bc815f</t>
+          <t>7bd733e818b9</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>60d4099fa8e8</t>
+          <t>d3fa5ad79bf5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>97c33b4867df</t>
+          <t>3a36ceba0867</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>26af2a5deb36</t>
+          <t>33e2483ac677</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2caf7010bfe8</t>
+          <t>ee0a2bf12529</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>d8a9af92de7e</t>
+          <t>717881bc815f</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>117a603c4cd5</t>
+          <t>60d4099fa8e8</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7c096f94f7ec</t>
+          <t>97c33b4867df</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>deecbd5d85c9</t>
+          <t>26af2a5deb36</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>8a0b21198503</t>
+          <t>2caf7010bfe8</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>978c27c3b3a2</t>
+          <t>d8a9af92de7e</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3b0c1f3af544</t>
+          <t>117a603c4cd5</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>85865c15faa0</t>
+          <t>7c096f94f7ec</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>2026-07-09T19:38:24</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2fbc29783aa3</t>
+          <t>deecbd5d85c9</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>2026-07-09T19:38:24</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>bfb3ee045202</t>
+          <t>8a0b21198503</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>2026-07-09T19:38:24</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>668d929856c2</t>
+          <t>978c27c3b3a2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>2026-07-09T19:38:24</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>748ca9ca8a8c</t>
+          <t>3b0c1f3af544</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>2026-07-09T19:38:24</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0583ecf7e94a</t>
+          <t>85865c15faa0</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>d34106ce649b</t>
+          <t>2fbc29783aa3</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>a118d71078ce</t>
+          <t>bfb3ee045202</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2009f682b697</t>
+          <t>668d929856c2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>e4f58040975b</t>
+          <t>748ca9ca8a8c</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1a14f7bcf117</t>
+          <t>0583ecf7e94a</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>e2ad34d954b6</t>
+          <t>d34106ce649b</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>05d457c2646a</t>
+          <t>a118d71078ce</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>901cb485b14d</t>
+          <t>2009f682b697</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>542110585a25</t>
+          <t>e4f58040975b</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4af7909e5cc5</t>
+          <t>1a14f7bcf117</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>04483f7bba5b</t>
+          <t>e2ad34d954b6</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>a9925fb49174</t>
+          <t>05d457c2646a</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>c88a3a7915f3</t>
+          <t>901cb485b14d</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>f542551ab771</t>
+          <t>542110585a25</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>067b94e61898</t>
+          <t>4af7909e5cc5</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>07196ca2a434</t>
+          <t>04483f7bba5b</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>b563a333eea7</t>
+          <t>a9925fb49174</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>a61e04f3f5c6</t>
+          <t>c88a3a7915f3</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>469c9703b3df</t>
+          <t>f542551ab771</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>27140d4c6bde</t>
+          <t>067b94e61898</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2d94a5005698</t>
+          <t>07196ca2a434</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>91b7bc700a69</t>
+          <t>b563a333eea7</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>a5a2b51b231f</t>
+          <t>a61e04f3f5c6</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5160de3d49db</t>
+          <t>469c9703b3df</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>e447d2d2f86b</t>
+          <t>27140d4c6bde</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>661c5b133106</t>
+          <t>2d94a5005698</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>57ba3a50d373</t>
+          <t>91b7bc700a69</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>9acc5fa04c57</t>
+          <t>a5a2b51b231f</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3929,22 +3929,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5c5e4d5100be</t>
+          <t>5160de3d49db</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>verification_timestamp</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Department of Space (DOS)</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
     </row>
@@ -3956,22 +3956,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5c5e4d5100be</t>
+          <t>e447d2d2f86b</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>verification_timestamp</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Department of Space (DOS)</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5c5e4d5100be</t>
+          <t>661c5b133106</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>86e6d2078291</t>
+          <t>57ba3a50d373</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>49a6e128d608</t>
+          <t>9acc5fa04c57</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4064,22 +4064,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>b0d59286db4e</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>verification_timestamp</t>
+          <t>department</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>Department of Space (DOS)</t>
         </is>
       </c>
     </row>
@@ -4091,22 +4091,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>c04af3420d01</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>verification_timestamp</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>Department of Space (DOS)</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>846a1abfd779</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0832e070b04e</t>
+          <t>86e6d2078291</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>dc447cd2531c</t>
+          <t>49a6e128d608</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5c5e4d5100be</t>
+          <t>b0d59286db4e</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>verification_timestamp</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Department of Space (DOS)</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
     </row>
@@ -4226,22 +4226,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5c5e4d5100be</t>
+          <t>c04af3420d01</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>verification_timestamp</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Department of Space (DOS)</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
     </row>
@@ -4253,22 +4253,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5c5e4d5100be</t>
+          <t>846a1abfd779</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>verification_status</t>
+          <t>verification_timestamp</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Application Closed</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Verified with Official Website</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>37c79aae4c5a</t>
+          <t>0832e070b04e</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>06031f7f400f</t>
+          <t>dc447cd2531c</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4334,22 +4334,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6923e12d41c2</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>verification_timestamp</t>
+          <t>department</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>Department of Space (DOS)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
         </is>
       </c>
     </row>
@@ -4361,22 +4361,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>b4597beaee47</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>verification_timestamp</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>Department of Space (DOS)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
         </is>
       </c>
     </row>
@@ -4388,22 +4388,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>68f70c89b2da</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>verification_timestamp</t>
+          <t>verification_status</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>Application Closed</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:24</t>
+          <t>Verified with Official Website</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7008451b6823</t>
+          <t>37c79aae4c5a</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>933d12e64467</t>
+          <t>06031f7f400f</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>9e2df8658bc1</t>
+          <t>6923e12d41c2</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>6cdcca5431ba</t>
+          <t>b4597beaee47</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>331871284cde</t>
+          <t>68f70c89b2da</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>b1a5aa288fa4</t>
+          <t>7008451b6823</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1eda9ff9a510</t>
+          <t>933d12e64467</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>d564ebc0225a</t>
+          <t>9e2df8658bc1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2487ccd94d7e</t>
+          <t>6cdcca5431ba</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>e0144438670c</t>
+          <t>331871284cde</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4e52839c0ee4</t>
+          <t>b1a5aa288fa4</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>279a10e59d43</t>
+          <t>1eda9ff9a510</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4734,12 +4734,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:23</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>20ce9957b1ad</t>
+          <t>d564ebc0225a</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4749,24 +4749,24 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:23</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:23</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>8f0a7d9e4c32</t>
+          <t>2487ccd94d7e</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4776,24 +4776,24 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:23</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:23</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>f38847e85b8a</t>
+          <t>e0144438670c</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4803,24 +4803,24 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:23</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:23</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>d3fc6c6dc095</t>
+          <t>4e52839c0ee4</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4830,24 +4830,24 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:23</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:23</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>9118b7253cd9</t>
+          <t>279a10e59d43</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-07-09T19:43:23</t>
+          <t>2026-07-09T19:43:24</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>4de01320d5c2</t>
+          <t>20ce9957b1ad</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>08e8618085b3</t>
+          <t>8f0a7d9e4c32</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>88e01056b013</t>
+          <t>f38847e85b8a</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0c8ea4334e02</t>
+          <t>d3fc6c6dc095</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3e6f8ac6a05e</t>
+          <t>9118b7253cd9</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>17626a2c978b</t>
+          <t>4de01320d5c2</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7001efc2b162</t>
+          <t>08e8618085b3</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1d75640aef2e</t>
+          <t>88e01056b013</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0ea53ef1ddcb</t>
+          <t>0c8ea4334e02</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>676b36b21a4e</t>
+          <t>3e6f8ac6a05e</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>3ff84b4e7123</t>
+          <t>17626a2c978b</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>57a200e19328</t>
+          <t>7001efc2b162</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>775183f8cc22</t>
+          <t>1d75640aef2e</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>b7d81dd93d71</t>
+          <t>0ea53ef1ddcb</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>cb151a0e48f8</t>
+          <t>676b36b21a4e</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>af2630addb70</t>
+          <t>3ff84b4e7123</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>1c4bc32ab34f</t>
+          <t>57a200e19328</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>b1694a9500c1</t>
+          <t>775183f8cc22</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5355,216 +5355,216 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>2026-07-09T19:43:23</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5c5e4d5100be</t>
+          <t>b7d81dd93d71</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>verification_timestamp</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Department of Space (DOS)</t>
+          <t>2026-07-09T19:38:24</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
+          <t>2026-07-09T19:43:23</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>2026-07-09T19:43:23</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>5c5e4d5100be</t>
+          <t>cb151a0e48f8</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>verification_timestamp</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Department of Space (DOS)</t>
+          <t>2026-07-09T19:38:24</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
+          <t>2026-07-09T19:43:23</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:25</t>
+          <t>2026-07-09T19:43:23</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5c5e4d5100be</t>
+          <t>af2630addb70</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>verification_status</t>
+          <t>verification_timestamp</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Application Closed</t>
+          <t>2026-07-09T19:38:24</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Verified with Official Website</t>
+          <t>2026-07-09T19:43:23</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
+          <t>2026-07-09T19:43:23</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1c4bc32ab34f</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>verification_timestamp</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
           <t>2026-07-09T19:38:24</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>20ce9957b1ad</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>job_name</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>ISRO ISTRAC Recruitment 2026 (ISTRAC:02:2026) - Technical Assistant, Scientific Assistant, Technician-B and other posts</t>
-        </is>
-      </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>ISRO ISTRAC:02:2026: Recruitment to the posts of Technician 'B', Draughtsman 'B', Technical Assistant, Scientific Assist</t>
+          <t>2026-07-09T19:43:23</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
+          <t>2026-07-09T19:43:23</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>b1694a9500c1</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>verification_timestamp</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
           <t>2026-07-09T19:38:24</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>20ce9957b1ad</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Department of Space</t>
-        </is>
-      </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>ISRO Telemetry, Tracking and Command Network (ISTRAC)</t>
+          <t>2026-07-09T19:43:23</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>20ce9957b1ad</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>apply_link</t>
+          <t>department</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://www.isro.gov.in/Careers.html</t>
+          <t>Department of Space (DOS)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://www.isro.gov.in/ViewAllOpportunities.html</t>
+          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>20ce9957b1ad</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>verification_timestamp</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-07-09T19:37:59</t>
+          <t>Department of Space (DOS)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>Indian Institute of Space Science and Technology (IIST) , Thiruvananthapuram</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>2026-07-09T19:38:25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>20ce9957b1ad</t>
+          <t>5c5e4d5100be</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>verification_status</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>isro,bengaluru,technical</t>
+          <t>Application Closed</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>isro,space,central,bengaluru</t>
+          <t>Verified with Official Website</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>f38847e85b8a</t>
+          <t>20ce9957b1ad</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ISRO ISTRAC Apprenticeship 2026 (ISTRAC:01:2026) - Graduate, Diploma and ITI Trade Apprentices</t>
+          <t>ISRO ISTRAC Recruitment 2026 (ISTRAC:02:2026) - Technical Assistant, Scientific Assistant, Technician-B and other posts</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>ISRO ISTRAC:01:2026: Recruitment to the posts of Graduate Apprentice Trainee,Diploma Apprentice Trainee,Diploma in Comme</t>
+          <t>ISRO ISTRAC:02:2026: Recruitment to the posts of Technician 'B', Draughtsman 'B', Technical Assistant, Scientific Assist</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>f38847e85b8a</t>
+          <t>20ce9957b1ad</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>f38847e85b8a</t>
+          <t>20ce9957b1ad</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>f38847e85b8a</t>
+          <t>20ce9957b1ad</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>f38847e85b8a</t>
+          <t>20ce9957b1ad</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>isro,apprentice,bengaluru,graduate apprentice</t>
+          <t>isro,bengaluru,technical</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>d3fc6c6dc095</t>
+          <t>f38847e85b8a</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5721,12 +5721,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ISRO URSC Junior Research Fellow (URSC:02:2026)</t>
+          <t>ISRO ISTRAC Apprenticeship 2026 (ISTRAC:01:2026) - Graduate, Diploma and ITI Trade Apprentices</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>ISRO URSC:02:2026: Recruitment to the posts of Junior Research Fellow (JRF)</t>
+          <t>ISRO ISTRAC:01:2026: Recruitment to the posts of Graduate Apprentice Trainee,Diploma Apprentice Trainee,Diploma in Comme</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>d3fc6c6dc095</t>
+          <t>f38847e85b8a</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>U R Rao Satellite Centre</t>
+          <t>Department of Space</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>U R Rao Satellite Centre,(URSC)</t>
+          <t>ISRO Telemetry, Tracking and Command Network (ISTRAC)</t>
         </is>
       </c>
     </row>
@@ -5765,18 +5765,22 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>d3fc6c6dc095</t>
+          <t>f38847e85b8a</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>application_start</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t>apply_link</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>https://www.isro.gov.in/Careers.html</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>https://www.isro.gov.in/ViewAllOpportunities.html</t>
         </is>
       </c>
     </row>
@@ -5788,22 +5792,22 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>d3fc6c6dc095</t>
+          <t>f38847e85b8a</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>apply_link</t>
+          <t>verification_timestamp</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://www.isro.gov.in/Careers.html</t>
+          <t>2026-07-09T19:37:59</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://www.isro.gov.in/ViewAllOpportunities.html</t>
+          <t>2026-07-09T19:38:24</t>
         </is>
       </c>
     </row>
@@ -5815,22 +5819,22 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>d3fc6c6dc095</t>
+          <t>f38847e85b8a</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>verification_timestamp</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-07-09T19:37:59</t>
+          <t>isro,apprentice,bengaluru,graduate apprentice</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-07-09T19:38:24</t>
+          <t>isro,space,central,bengaluru</t>
         </is>
       </c>
     </row>
@@ -5847,76 +5851,207 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>job_name</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>isro,research,jrf,bengaluru</t>
+          <t>ISRO URSC Junior Research Fellow (URSC:02:2026)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>isro,space,central,bengaluru</t>
+          <t>ISRO URSC:02:2026: Recruitment to the posts of Junior Research Fellow (JRF)</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-07-09T19:37:59</t>
+          <t>2026-07-09T19:38:24</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>95999fe15290</t>
+          <t>d3fc6c6dc095</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>department</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>U R Rao Satellite Centre</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>U R Rao Satellite Centre,(URSC)</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
+          <t>2026-07-09T19:38:24</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>d3fc6c6dc095</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>application_start</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-07-09T19:38:24</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>d3fc6c6dc095</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>apply_link</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>https://www.isro.gov.in/Careers.html</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.isro.gov.in/ViewAllOpportunities.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-07-09T19:38:24</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>d3fc6c6dc095</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>verification_timestamp</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
           <t>2026-07-09T19:37:59</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-07-09T19:38:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-07-09T19:38:24</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>d3fc6c6dc095</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>isro,research,jrf,bengaluru</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>isro,space,central,bengaluru</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-07-09T19:37:59</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>95999fe15290</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-07-09T19:37:59</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
         <is>
           <t>97971372922f</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="C201" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t>Applied</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="E201" t="inlineStr">
         <is>
           <t>Applied</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E196"/>
+  <autoFilter ref="A1:E201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6227,7 +6362,7 @@
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB2" s="5" t="n">
@@ -6251,7 +6386,7 @@
       </c>
       <c r="AG2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6477,7 @@
       </c>
       <c r="AA3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB3" s="7" t="n">
@@ -6370,7 +6505,7 @@
       </c>
       <c r="AG3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6612,7 @@
       </c>
       <c r="AA4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB4" s="7" t="n">
@@ -6501,7 +6636,7 @@
       </c>
       <c r="AG4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6779,7 @@
       </c>
       <c r="AG5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6914,7 @@
       </c>
       <c r="AG6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -6918,7 +7053,7 @@
       </c>
       <c r="AG7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7184,7 @@
       </c>
       <c r="AG8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7311,7 @@
       </c>
       <c r="AG9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7458,7 @@
       </c>
       <c r="AG10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7585,7 @@
       </c>
       <c r="AG11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7688,7 @@
       </c>
       <c r="AA12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB12" s="7" t="n">
@@ -7577,7 +7712,7 @@
       </c>
       <c r="AG12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7851,7 @@
       </c>
       <c r="AG13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7982,7 @@
       </c>
       <c r="AG14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -7986,7 +8121,7 @@
       </c>
       <c r="AG15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8246,7 @@
       </c>
       <c r="AG16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8367,7 @@
       </c>
       <c r="AG17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -8349,7 +8484,7 @@
       </c>
       <c r="AG18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8609,7 @@
       </c>
       <c r="AG19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8726,7 @@
       </c>
       <c r="AG20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8843,7 @@
       </c>
       <c r="AG21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -8825,7 +8960,7 @@
       </c>
       <c r="AG22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -8946,7 +9081,7 @@
       </c>
       <c r="AG23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9198,7 @@
       </c>
       <c r="AG24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9315,7 @@
       </c>
       <c r="AG25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9396,7 @@
       </c>
       <c r="AA26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB26" s="9" t="n">
@@ -9289,7 +9424,7 @@
       </c>
       <c r="AG26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -9370,7 +9505,7 @@
       </c>
       <c r="AA27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB27" s="9" t="n">
@@ -9398,7 +9533,7 @@
       </c>
       <c r="AG27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9614,7 @@
       </c>
       <c r="AA28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB28" s="9" t="n">
@@ -9507,7 +9642,7 @@
       </c>
       <c r="AG28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9723,7 @@
       </c>
       <c r="AA29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB29" s="9" t="n">
@@ -9616,7 +9751,7 @@
       </c>
       <c r="AG29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9832,7 @@
       </c>
       <c r="AA30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB30" s="9" t="n">
@@ -9725,7 +9860,7 @@
       </c>
       <c r="AG30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9945,7 @@
       </c>
       <c r="AA31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB31" s="9" t="n">
@@ -9838,7 +9973,7 @@
       </c>
       <c r="AG31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -9919,7 +10054,7 @@
       </c>
       <c r="AA32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB32" s="9" t="n">
@@ -9947,7 +10082,7 @@
       </c>
       <c r="AG32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -10028,7 +10163,7 @@
       </c>
       <c r="AA33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB33" s="9" t="n">
@@ -10056,7 +10191,7 @@
       </c>
       <c r="AG33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10272,7 @@
       </c>
       <c r="AA34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB34" s="9" t="n">
@@ -10165,7 +10300,7 @@
       </c>
       <c r="AG34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10381,7 @@
       </c>
       <c r="AA35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB35" s="9" t="n">
@@ -10274,7 +10409,7 @@
       </c>
       <c r="AG35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10490,7 @@
       </c>
       <c r="AA36" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB36" s="9" t="n">
@@ -10383,7 +10518,7 @@
       </c>
       <c r="AG36" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10603,7 @@
       </c>
       <c r="AA37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB37" s="9" t="n">
@@ -10496,7 +10631,7 @@
       </c>
       <c r="AG37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10712,7 @@
       </c>
       <c r="AA38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB38" s="9" t="n">
@@ -10605,7 +10740,7 @@
       </c>
       <c r="AG38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -10686,7 +10821,7 @@
       </c>
       <c r="AA39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB39" s="9" t="n">
@@ -10714,7 +10849,7 @@
       </c>
       <c r="AG39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -10795,7 +10930,7 @@
       </c>
       <c r="AA40" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB40" s="9" t="n">
@@ -10823,7 +10958,7 @@
       </c>
       <c r="AG40" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -10904,7 +11039,7 @@
       </c>
       <c r="AA41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB41" s="9" t="n">
@@ -10932,7 +11067,7 @@
       </c>
       <c r="AG41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -11013,7 +11148,7 @@
       </c>
       <c r="AA42" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB42" s="9" t="n">
@@ -11041,7 +11176,7 @@
       </c>
       <c r="AG42" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11257,7 @@
       </c>
       <c r="AA43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB43" s="9" t="n">
@@ -11150,7 +11285,7 @@
       </c>
       <c r="AG43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -11231,7 +11366,7 @@
       </c>
       <c r="AA44" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB44" s="9" t="n">
@@ -11259,7 +11394,7 @@
       </c>
       <c r="AG44" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11475,7 @@
       </c>
       <c r="AA45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB45" s="9" t="n">
@@ -11368,7 +11503,7 @@
       </c>
       <c r="AG45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -11449,7 +11584,7 @@
       </c>
       <c r="AA46" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB46" s="9" t="n">
@@ -11477,7 +11612,7 @@
       </c>
       <c r="AG46" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11693,7 @@
       </c>
       <c r="AA47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB47" s="9" t="n">
@@ -11586,7 +11721,7 @@
       </c>
       <c r="AG47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -11667,7 +11802,7 @@
       </c>
       <c r="AA48" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB48" s="9" t="n">
@@ -11695,7 +11830,7 @@
       </c>
       <c r="AG48" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -11776,7 +11911,7 @@
       </c>
       <c r="AA49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB49" s="9" t="n">
@@ -11804,7 +11939,7 @@
       </c>
       <c r="AG49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -11885,7 +12020,7 @@
       </c>
       <c r="AA50" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB50" s="9" t="n">
@@ -11913,7 +12048,7 @@
       </c>
       <c r="AG50" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -11994,7 +12129,7 @@
       </c>
       <c r="AA51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB51" s="9" t="n">
@@ -12022,7 +12157,7 @@
       </c>
       <c r="AG51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -12103,7 +12238,7 @@
       </c>
       <c r="AA52" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB52" s="9" t="n">
@@ -12131,7 +12266,7 @@
       </c>
       <c r="AG52" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12347,7 @@
       </c>
       <c r="AA53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB53" s="9" t="n">
@@ -12240,7 +12375,7 @@
       </c>
       <c r="AG53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -12321,7 +12456,7 @@
       </c>
       <c r="AA54" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB54" s="9" t="n">
@@ -12349,7 +12484,7 @@
       </c>
       <c r="AG54" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12565,7 @@
       </c>
       <c r="AA55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB55" s="9" t="n">
@@ -12458,7 +12593,7 @@
       </c>
       <c r="AG55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12674,7 @@
       </c>
       <c r="AA56" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB56" s="9" t="n">
@@ -12567,7 +12702,7 @@
       </c>
       <c r="AG56" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12783,7 @@
       </c>
       <c r="AA57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB57" s="9" t="n">
@@ -12676,7 +12811,7 @@
       </c>
       <c r="AG57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -12757,7 +12892,7 @@
       </c>
       <c r="AA58" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB58" s="9" t="n">
@@ -12785,7 +12920,7 @@
       </c>
       <c r="AG58" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -12866,7 +13001,7 @@
       </c>
       <c r="AA59" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB59" s="9" t="n">
@@ -12894,7 +13029,7 @@
       </c>
       <c r="AG59" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -12975,7 +13110,7 @@
       </c>
       <c r="AA60" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB60" s="9" t="n">
@@ -13003,7 +13138,7 @@
       </c>
       <c r="AG60" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -13112,7 +13247,7 @@
       </c>
       <c r="AG61" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -13217,7 +13352,7 @@
       </c>
       <c r="AG62" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -13322,7 +13457,7 @@
       </c>
       <c r="AG63" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -13427,7 +13562,7 @@
       </c>
       <c r="AG64" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -13532,7 +13667,7 @@
       </c>
       <c r="AG65" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13776,7 @@
       </c>
       <c r="AG66" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -13746,7 +13881,7 @@
       </c>
       <c r="AG67" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -13855,7 +13990,7 @@
       </c>
       <c r="AG68" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -13960,7 +14095,7 @@
       </c>
       <c r="AG69" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14200,7 @@
       </c>
       <c r="AG70" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14305,7 @@
       </c>
       <c r="AG71" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -14275,7 +14410,7 @@
       </c>
       <c r="AG72" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14515,7 @@
       </c>
       <c r="AG73" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -14485,7 +14620,7 @@
       </c>
       <c r="AG74" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -14590,7 +14725,7 @@
       </c>
       <c r="AG75" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -14695,7 +14830,7 @@
       </c>
       <c r="AG76" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -14800,7 +14935,7 @@
       </c>
       <c r="AG77" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -14905,7 +15040,7 @@
       </c>
       <c r="AG78" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -15010,7 +15145,7 @@
       </c>
       <c r="AG79" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -15115,7 +15250,7 @@
       </c>
       <c r="AG80" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -15220,7 +15355,7 @@
       </c>
       <c r="AG81" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -15325,7 +15460,7 @@
       </c>
       <c r="AG82" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -15430,7 +15565,7 @@
       </c>
       <c r="AG83" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -15535,7 +15670,7 @@
       </c>
       <c r="AG84" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -15640,7 +15775,7 @@
       </c>
       <c r="AG85" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -15745,7 +15880,7 @@
       </c>
       <c r="AG86" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -15850,7 +15985,7 @@
       </c>
       <c r="AG87" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -15955,7 +16090,7 @@
       </c>
       <c r="AG88" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -16060,7 +16195,7 @@
       </c>
       <c r="AG89" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -16165,7 +16300,7 @@
       </c>
       <c r="AG90" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -16270,7 +16405,7 @@
       </c>
       <c r="AG91" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -16375,7 +16510,7 @@
       </c>
       <c r="AG92" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -16480,7 +16615,7 @@
       </c>
       <c r="AG93" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16720,7 @@
       </c>
       <c r="AG94" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -16690,7 +16825,7 @@
       </c>
       <c r="AG95" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -16795,7 +16930,7 @@
       </c>
       <c r="AG96" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -16900,7 +17035,7 @@
       </c>
       <c r="AG97" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -17005,7 +17140,7 @@
       </c>
       <c r="AG98" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17245,7 @@
       </c>
       <c r="AG99" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -17215,7 +17350,7 @@
       </c>
       <c r="AG100" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -17320,7 +17455,7 @@
       </c>
       <c r="AG101" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -17425,7 +17560,7 @@
       </c>
       <c r="AG102" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -17530,7 +17665,7 @@
       </c>
       <c r="AG103" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -17635,7 +17770,7 @@
       </c>
       <c r="AG104" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17875,7 @@
       </c>
       <c r="AG105" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -17845,7 +17980,7 @@
       </c>
       <c r="AG106" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -17950,7 +18085,7 @@
       </c>
       <c r="AG107" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -18055,7 +18190,7 @@
       </c>
       <c r="AG108" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -18160,7 +18295,7 @@
       </c>
       <c r="AG109" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -18265,7 +18400,7 @@
       </c>
       <c r="AG110" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -18370,7 +18505,7 @@
       </c>
       <c r="AG111" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -18475,7 +18610,7 @@
       </c>
       <c r="AG112" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -18560,7 +18695,7 @@
       </c>
       <c r="AA113" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB113" s="9" t="n">
@@ -18584,7 +18719,7 @@
       </c>
       <c r="AG113" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18800,7 @@
       </c>
       <c r="AA114" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB114" s="9" t="n">
@@ -18689,7 +18824,7 @@
       </c>
       <c r="AG114" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18909,7 @@
       </c>
       <c r="AA115" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB115" s="9" t="n">
@@ -18798,7 +18933,7 @@
       </c>
       <c r="AG115" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -18879,7 +19014,7 @@
       </c>
       <c r="AA116" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB116" s="9" t="n">
@@ -18903,7 +19038,7 @@
       </c>
       <c r="AG116" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -18984,7 +19119,7 @@
       </c>
       <c r="AA117" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB117" s="9" t="n">
@@ -19008,7 +19143,7 @@
       </c>
       <c r="AG117" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -19089,7 +19224,7 @@
       </c>
       <c r="AA118" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB118" s="9" t="n">
@@ -19113,7 +19248,7 @@
       </c>
       <c r="AG118" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -19194,7 +19329,7 @@
       </c>
       <c r="AA119" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB119" s="9" t="n">
@@ -19218,7 +19353,7 @@
       </c>
       <c r="AG119" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19434,7 @@
       </c>
       <c r="AA120" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB120" s="9" t="n">
@@ -19323,7 +19458,7 @@
       </c>
       <c r="AG120" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -19404,7 +19539,7 @@
       </c>
       <c r="AA121" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB121" s="9" t="n">
@@ -19428,7 +19563,7 @@
       </c>
       <c r="AG121" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19644,7 @@
       </c>
       <c r="AA122" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB122" s="9" t="n">
@@ -19533,7 +19668,7 @@
       </c>
       <c r="AG122" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -19614,7 +19749,7 @@
       </c>
       <c r="AA123" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB123" s="9" t="n">
@@ -19638,7 +19773,7 @@
       </c>
       <c r="AG123" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -19743,7 +19878,7 @@
       </c>
       <c r="AG124" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19983,7 @@
       </c>
       <c r="AG125" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20517,7 @@
       </c>
       <c r="AA2" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB2" s="9" t="n">
@@ -20410,7 +20545,7 @@
       </c>
       <c r="AG2" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -20471,7 +20606,7 @@
       </c>
       <c r="AA3" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB3" s="9" t="n">
@@ -20499,7 +20634,7 @@
       </c>
       <c r="AG3" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -20572,7 +20707,7 @@
       </c>
       <c r="AA4" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB4" s="9" t="n">
@@ -20600,7 +20735,7 @@
       </c>
       <c r="AG4" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -20673,7 +20808,7 @@
       </c>
       <c r="AA5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB5" s="9" t="n">
@@ -20701,7 +20836,7 @@
       </c>
       <c r="AG5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20909,7 @@
       </c>
       <c r="AA6" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB6" s="9" t="n">
@@ -20802,7 +20937,7 @@
       </c>
       <c r="AG6" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -20875,7 +21010,7 @@
       </c>
       <c r="AA7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB7" s="9" t="n">
@@ -20903,7 +21038,7 @@
       </c>
       <c r="AG7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -20976,7 +21111,7 @@
       </c>
       <c r="AA8" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB8" s="9" t="n">
@@ -21004,7 +21139,7 @@
       </c>
       <c r="AG8" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -21077,7 +21212,7 @@
       </c>
       <c r="AA9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB9" s="9" t="n">
@@ -21105,7 +21240,7 @@
       </c>
       <c r="AG9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -21178,7 +21313,7 @@
       </c>
       <c r="AA10" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB10" s="9" t="n">
@@ -21206,7 +21341,7 @@
       </c>
       <c r="AG10" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -21279,7 +21414,7 @@
       </c>
       <c r="AA11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB11" s="9" t="n">
@@ -21307,7 +21442,7 @@
       </c>
       <c r="AG11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -21380,7 +21515,7 @@
       </c>
       <c r="AA12" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB12" s="9" t="n">
@@ -21408,7 +21543,7 @@
       </c>
       <c r="AG12" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -21481,7 +21616,7 @@
       </c>
       <c r="AA13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB13" s="9" t="n">
@@ -21509,7 +21644,7 @@
       </c>
       <c r="AG13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -21582,7 +21717,7 @@
       </c>
       <c r="AA14" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB14" s="9" t="n">
@@ -21610,7 +21745,7 @@
       </c>
       <c r="AG14" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -21683,7 +21818,7 @@
       </c>
       <c r="AA15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB15" s="9" t="n">
@@ -21711,7 +21846,7 @@
       </c>
       <c r="AG15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -21784,7 +21919,7 @@
       </c>
       <c r="AA16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB16" s="9" t="n">
@@ -21812,7 +21947,7 @@
       </c>
       <c r="AG16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -21885,7 +22020,7 @@
       </c>
       <c r="AA17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB17" s="9" t="n">
@@ -21913,7 +22048,7 @@
       </c>
       <c r="AG17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -21986,7 +22121,7 @@
       </c>
       <c r="AA18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB18" s="9" t="n">
@@ -22014,7 +22149,7 @@
       </c>
       <c r="AG18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -22087,7 +22222,7 @@
       </c>
       <c r="AA19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB19" s="9" t="n">
@@ -22115,7 +22250,7 @@
       </c>
       <c r="AG19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -22188,7 +22323,7 @@
       </c>
       <c r="AA20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB20" s="9" t="n">
@@ -22216,7 +22351,7 @@
       </c>
       <c r="AG20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -22289,7 +22424,7 @@
       </c>
       <c r="AA21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB21" s="9" t="n">
@@ -22317,7 +22452,7 @@
       </c>
       <c r="AG21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -22390,7 +22525,7 @@
       </c>
       <c r="AA22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB22" s="9" t="n">
@@ -22418,7 +22553,7 @@
       </c>
       <c r="AG22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22626,7 @@
       </c>
       <c r="AA23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB23" s="9" t="n">
@@ -22519,7 +22654,7 @@
       </c>
       <c r="AG23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -22592,7 +22727,7 @@
       </c>
       <c r="AA24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB24" s="9" t="n">
@@ -22620,7 +22755,7 @@
       </c>
       <c r="AG24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -22693,7 +22828,7 @@
       </c>
       <c r="AA25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB25" s="9" t="n">
@@ -22721,7 +22856,7 @@
       </c>
       <c r="AG25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -22794,7 +22929,7 @@
       </c>
       <c r="AA26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB26" s="9" t="n">
@@ -22822,7 +22957,7 @@
       </c>
       <c r="AG26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -22895,7 +23030,7 @@
       </c>
       <c r="AA27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB27" s="9" t="n">
@@ -22923,7 +23058,7 @@
       </c>
       <c r="AG27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -22996,7 +23131,7 @@
       </c>
       <c r="AA28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB28" s="9" t="n">
@@ -23024,7 +23159,7 @@
       </c>
       <c r="AG28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -23421,7 +23556,7 @@
       </c>
       <c r="AG2" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -23556,7 +23691,7 @@
       </c>
       <c r="AG3" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -23878,7 +24013,7 @@
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB2" s="5" t="n">
@@ -23902,7 +24037,7 @@
       </c>
       <c r="AG2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -23993,7 +24128,7 @@
       </c>
       <c r="AA3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB3" s="7" t="n">
@@ -24021,7 +24156,7 @@
       </c>
       <c r="AG3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -24128,7 +24263,7 @@
       </c>
       <c r="AA4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB4" s="7" t="n">
@@ -24152,7 +24287,7 @@
       </c>
       <c r="AG4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -24287,7 +24422,7 @@
       </c>
       <c r="AG5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -24426,7 +24561,7 @@
       </c>
       <c r="AG6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24692,7 @@
       </c>
       <c r="AG7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -24684,7 +24819,7 @@
       </c>
       <c r="AG8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -24831,7 +24966,7 @@
       </c>
       <c r="AG9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -24958,7 +25093,7 @@
       </c>
       <c r="AG10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -25061,7 +25196,7 @@
       </c>
       <c r="AA11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB11" s="7" t="n">
@@ -25085,7 +25220,7 @@
       </c>
       <c r="AG11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -25216,7 +25351,7 @@
       </c>
       <c r="AG12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -25355,7 +25490,7 @@
       </c>
       <c r="AG13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -25506,7 +25641,7 @@
       </c>
       <c r="AG14" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -25623,7 +25758,7 @@
       </c>
       <c r="AG15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -25740,7 +25875,7 @@
       </c>
       <c r="AG16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -25857,7 +25992,7 @@
       </c>
       <c r="AG17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -25948,7 +26083,7 @@
       </c>
       <c r="AA18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB18" s="9" t="n">
@@ -25976,7 +26111,7 @@
       </c>
       <c r="AG18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26202,7 @@
       </c>
       <c r="AA19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB19" s="9" t="n">
@@ -26095,7 +26230,7 @@
       </c>
       <c r="AG19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -26176,7 +26311,7 @@
       </c>
       <c r="AA20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB20" s="9" t="n">
@@ -26204,7 +26339,7 @@
       </c>
       <c r="AG20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -26295,7 +26430,7 @@
       </c>
       <c r="AA21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB21" s="9" t="n">
@@ -26323,7 +26458,7 @@
       </c>
       <c r="AG21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26539,7 @@
       </c>
       <c r="AA22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB22" s="9" t="n">
@@ -26432,7 +26567,7 @@
       </c>
       <c r="AG22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -26523,7 +26658,7 @@
       </c>
       <c r="AA23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB23" s="9" t="n">
@@ -26551,7 +26686,7 @@
       </c>
       <c r="AG23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -26642,7 +26777,7 @@
       </c>
       <c r="AA24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB24" s="9" t="n">
@@ -26670,7 +26805,7 @@
       </c>
       <c r="AG24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -26751,7 +26886,7 @@
       </c>
       <c r="AA25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB25" s="9" t="n">
@@ -26779,7 +26914,7 @@
       </c>
       <c r="AG25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -26860,7 +26995,7 @@
       </c>
       <c r="AA26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB26" s="9" t="n">
@@ -26888,7 +27023,7 @@
       </c>
       <c r="AG26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -26969,7 +27104,7 @@
       </c>
       <c r="AA27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB27" s="9" t="n">
@@ -26997,7 +27132,7 @@
       </c>
       <c r="AG27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -27088,7 +27223,7 @@
       </c>
       <c r="AA28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB28" s="9" t="n">
@@ -27116,7 +27251,7 @@
       </c>
       <c r="AG28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -27207,7 +27342,7 @@
       </c>
       <c r="AA29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB29" s="9" t="n">
@@ -27235,7 +27370,7 @@
       </c>
       <c r="AG29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -27320,7 +27455,7 @@
       </c>
       <c r="AA30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB30" s="9" t="n">
@@ -27348,7 +27483,7 @@
       </c>
       <c r="AG30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -27439,7 +27574,7 @@
       </c>
       <c r="AA31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB31" s="9" t="n">
@@ -27467,7 +27602,7 @@
       </c>
       <c r="AG31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -27558,7 +27693,7 @@
       </c>
       <c r="AA32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB32" s="9" t="n">
@@ -27586,7 +27721,7 @@
       </c>
       <c r="AG32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -27677,7 +27812,7 @@
       </c>
       <c r="AA33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB33" s="9" t="n">
@@ -27705,7 +27840,7 @@
       </c>
       <c r="AG33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -27796,7 +27931,7 @@
       </c>
       <c r="AA34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB34" s="9" t="n">
@@ -27824,7 +27959,7 @@
       </c>
       <c r="AG34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -27915,7 +28050,7 @@
       </c>
       <c r="AA35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB35" s="9" t="n">
@@ -27943,7 +28078,7 @@
       </c>
       <c r="AG35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28169,7 @@
       </c>
       <c r="AA36" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB36" s="9" t="n">
@@ -28062,7 +28197,7 @@
       </c>
       <c r="AG36" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -28143,7 +28278,7 @@
       </c>
       <c r="AA37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB37" s="9" t="n">
@@ -28171,7 +28306,7 @@
       </c>
       <c r="AG37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -28262,7 +28397,7 @@
       </c>
       <c r="AA38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB38" s="9" t="n">
@@ -28290,7 +28425,7 @@
       </c>
       <c r="AG38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -28371,7 +28506,7 @@
       </c>
       <c r="AA39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB39" s="9" t="n">
@@ -28399,7 +28534,7 @@
       </c>
       <c r="AG39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -28480,7 +28615,7 @@
       </c>
       <c r="AA40" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB40" s="9" t="n">
@@ -28508,7 +28643,7 @@
       </c>
       <c r="AG40" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -28599,7 +28734,7 @@
       </c>
       <c r="AA41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB41" s="9" t="n">
@@ -28627,7 +28762,7 @@
       </c>
       <c r="AG41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -28708,7 +28843,7 @@
       </c>
       <c r="AA42" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB42" s="9" t="n">
@@ -28736,7 +28871,7 @@
       </c>
       <c r="AG42" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -28817,7 +28952,7 @@
       </c>
       <c r="AA43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB43" s="9" t="n">
@@ -28845,7 +28980,7 @@
       </c>
       <c r="AG43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -28936,7 +29071,7 @@
       </c>
       <c r="AA44" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB44" s="9" t="n">
@@ -28964,7 +29099,7 @@
       </c>
       <c r="AG44" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -29055,7 +29190,7 @@
       </c>
       <c r="AA45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB45" s="9" t="n">
@@ -29083,7 +29218,7 @@
       </c>
       <c r="AG45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -29168,7 +29303,7 @@
       </c>
       <c r="AA46" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB46" s="9" t="n">
@@ -29196,7 +29331,7 @@
       </c>
       <c r="AG46" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -29287,7 +29422,7 @@
       </c>
       <c r="AA47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB47" s="9" t="n">
@@ -29315,7 +29450,7 @@
       </c>
       <c r="AG47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -29406,7 +29541,7 @@
       </c>
       <c r="AA48" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB48" s="9" t="n">
@@ -29434,7 +29569,7 @@
       </c>
       <c r="AG48" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -29525,7 +29660,7 @@
       </c>
       <c r="AA49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB49" s="9" t="n">
@@ -29553,7 +29688,7 @@
       </c>
       <c r="AG49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -29644,7 +29779,7 @@
       </c>
       <c r="AA50" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB50" s="9" t="n">
@@ -29672,7 +29807,7 @@
       </c>
       <c r="AG50" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -29763,7 +29898,7 @@
       </c>
       <c r="AA51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB51" s="9" t="n">
@@ -29791,7 +29926,7 @@
       </c>
       <c r="AG51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -29882,7 +30017,7 @@
       </c>
       <c r="AA52" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB52" s="9" t="n">
@@ -29910,7 +30045,7 @@
       </c>
       <c r="AG52" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -30001,7 +30136,7 @@
       </c>
       <c r="AA53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB53" s="9" t="n">
@@ -30029,7 +30164,7 @@
       </c>
       <c r="AG53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -30120,7 +30255,7 @@
       </c>
       <c r="AA54" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB54" s="9" t="n">
@@ -30148,7 +30283,7 @@
       </c>
       <c r="AG54" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -30239,7 +30374,7 @@
       </c>
       <c r="AA55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB55" s="9" t="n">
@@ -30267,7 +30402,7 @@
       </c>
       <c r="AG55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -30358,7 +30493,7 @@
       </c>
       <c r="AA56" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB56" s="9" t="n">
@@ -30386,7 +30521,7 @@
       </c>
       <c r="AG56" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -30477,7 +30612,7 @@
       </c>
       <c r="AA57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB57" s="9" t="n">
@@ -30505,7 +30640,7 @@
       </c>
       <c r="AG57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -30596,7 +30731,7 @@
       </c>
       <c r="AA58" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB58" s="9" t="n">
@@ -30624,7 +30759,7 @@
       </c>
       <c r="AG58" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -30715,7 +30850,7 @@
       </c>
       <c r="AA59" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB59" s="9" t="n">
@@ -30743,7 +30878,7 @@
       </c>
       <c r="AG59" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30969,7 @@
       </c>
       <c r="AA60" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB60" s="9" t="n">
@@ -30862,7 +30997,7 @@
       </c>
       <c r="AG60" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -30953,7 +31088,7 @@
       </c>
       <c r="AA61" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB61" s="9" t="n">
@@ -30981,7 +31116,7 @@
       </c>
       <c r="AG61" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -31072,7 +31207,7 @@
       </c>
       <c r="AA62" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB62" s="9" t="n">
@@ -31100,7 +31235,7 @@
       </c>
       <c r="AG62" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -31191,7 +31326,7 @@
       </c>
       <c r="AA63" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB63" s="9" t="n">
@@ -31219,7 +31354,7 @@
       </c>
       <c r="AG63" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -31310,7 +31445,7 @@
       </c>
       <c r="AA64" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB64" s="9" t="n">
@@ -31338,7 +31473,7 @@
       </c>
       <c r="AG64" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -31429,7 +31564,7 @@
       </c>
       <c r="AA65" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB65" s="9" t="n">
@@ -31457,7 +31592,7 @@
       </c>
       <c r="AG65" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -31548,7 +31683,7 @@
       </c>
       <c r="AA66" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB66" s="9" t="n">
@@ -31576,7 +31711,7 @@
       </c>
       <c r="AG66" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -31667,7 +31802,7 @@
       </c>
       <c r="AA67" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB67" s="9" t="n">
@@ -31695,7 +31830,7 @@
       </c>
       <c r="AG67" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -31786,7 +31921,7 @@
       </c>
       <c r="AA68" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB68" s="9" t="n">
@@ -31814,7 +31949,7 @@
       </c>
       <c r="AG68" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -31905,7 +32040,7 @@
       </c>
       <c r="AA69" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB69" s="9" t="n">
@@ -31933,7 +32068,7 @@
       </c>
       <c r="AG69" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -32024,7 +32159,7 @@
       </c>
       <c r="AA70" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB70" s="9" t="n">
@@ -32052,7 +32187,7 @@
       </c>
       <c r="AG70" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -32143,7 +32278,7 @@
       </c>
       <c r="AA71" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB71" s="9" t="n">
@@ -32171,7 +32306,7 @@
       </c>
       <c r="AG71" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -32258,7 +32393,7 @@
       </c>
       <c r="AA72" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB72" s="9" t="n">
@@ -32286,7 +32421,7 @@
       </c>
       <c r="AG72" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -32377,7 +32512,7 @@
       </c>
       <c r="AA73" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB73" s="9" t="n">
@@ -32405,7 +32540,7 @@
       </c>
       <c r="AG73" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -32496,7 +32631,7 @@
       </c>
       <c r="AA74" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB74" s="9" t="n">
@@ -32524,7 +32659,7 @@
       </c>
       <c r="AG74" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -32615,7 +32750,7 @@
       </c>
       <c r="AA75" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB75" s="9" t="n">
@@ -32643,7 +32778,7 @@
       </c>
       <c r="AG75" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -32724,7 +32859,7 @@
       </c>
       <c r="AA76" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB76" s="9" t="n">
@@ -32752,7 +32887,7 @@
       </c>
       <c r="AG76" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -32833,7 +32968,7 @@
       </c>
       <c r="AA77" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB77" s="9" t="n">
@@ -32861,7 +32996,7 @@
       </c>
       <c r="AG77" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -32942,7 +33077,7 @@
       </c>
       <c r="AA78" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB78" s="9" t="n">
@@ -32970,7 +33105,7 @@
       </c>
       <c r="AG78" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -33051,7 +33186,7 @@
       </c>
       <c r="AA79" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB79" s="9" t="n">
@@ -33079,7 +33214,7 @@
       </c>
       <c r="AG79" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -33160,7 +33295,7 @@
       </c>
       <c r="AA80" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB80" s="9" t="n">
@@ -33188,7 +33323,7 @@
       </c>
       <c r="AG80" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -33269,7 +33404,7 @@
       </c>
       <c r="AA81" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB81" s="9" t="n">
@@ -33297,7 +33432,7 @@
       </c>
       <c r="AG81" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -33378,7 +33513,7 @@
       </c>
       <c r="AA82" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB82" s="9" t="n">
@@ -33406,7 +33541,7 @@
       </c>
       <c r="AG82" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33622,7 @@
       </c>
       <c r="AA83" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB83" s="9" t="n">
@@ -33515,7 +33650,7 @@
       </c>
       <c r="AG83" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -33606,7 +33741,7 @@
       </c>
       <c r="AA84" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB84" s="9" t="n">
@@ -33634,7 +33769,7 @@
       </c>
       <c r="AG84" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -33725,7 +33860,7 @@
       </c>
       <c r="AA85" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB85" s="9" t="n">
@@ -33753,7 +33888,7 @@
       </c>
       <c r="AG85" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -33834,7 +33969,7 @@
       </c>
       <c r="AA86" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB86" s="9" t="n">
@@ -33862,7 +33997,7 @@
       </c>
       <c r="AG86" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -33943,7 +34078,7 @@
       </c>
       <c r="AA87" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB87" s="9" t="n">
@@ -33971,7 +34106,7 @@
       </c>
       <c r="AG87" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -34058,7 +34193,7 @@
       </c>
       <c r="AA88" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB88" s="9" t="n">
@@ -34086,7 +34221,7 @@
       </c>
       <c r="AG88" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -34167,7 +34302,7 @@
       </c>
       <c r="AA89" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB89" s="9" t="n">
@@ -34195,7 +34330,7 @@
       </c>
       <c r="AG89" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -34282,7 +34417,7 @@
       </c>
       <c r="AA90" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB90" s="9" t="n">
@@ -34310,7 +34445,7 @@
       </c>
       <c r="AG90" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -34391,7 +34526,7 @@
       </c>
       <c r="AA91" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB91" s="9" t="n">
@@ -34419,7 +34554,7 @@
       </c>
       <c r="AG91" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -34500,7 +34635,7 @@
       </c>
       <c r="AA92" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB92" s="9" t="n">
@@ -34528,7 +34663,7 @@
       </c>
       <c r="AG92" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -34619,7 +34754,7 @@
       </c>
       <c r="AA93" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB93" s="9" t="n">
@@ -34647,7 +34782,7 @@
       </c>
       <c r="AG93" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -34728,7 +34863,7 @@
       </c>
       <c r="AA94" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB94" s="9" t="n">
@@ -34756,7 +34891,7 @@
       </c>
       <c r="AG94" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -34837,7 +34972,7 @@
       </c>
       <c r="AA95" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB95" s="9" t="n">
@@ -34865,7 +35000,7 @@
       </c>
       <c r="AG95" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -34946,7 +35081,7 @@
       </c>
       <c r="AA96" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB96" s="9" t="n">
@@ -34974,7 +35109,7 @@
       </c>
       <c r="AG96" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -35055,7 +35190,7 @@
       </c>
       <c r="AA97" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB97" s="9" t="n">
@@ -35083,7 +35218,7 @@
       </c>
       <c r="AG97" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -35164,7 +35299,7 @@
       </c>
       <c r="AA98" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB98" s="9" t="n">
@@ -35192,7 +35327,7 @@
       </c>
       <c r="AG98" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -35273,7 +35408,7 @@
       </c>
       <c r="AA99" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB99" s="9" t="n">
@@ -35301,7 +35436,7 @@
       </c>
       <c r="AG99" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -35388,7 +35523,7 @@
       </c>
       <c r="AA100" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB100" s="9" t="n">
@@ -35416,7 +35551,7 @@
       </c>
       <c r="AG100" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -35497,7 +35632,7 @@
       </c>
       <c r="AA101" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB101" s="9" t="n">
@@ -35525,7 +35660,7 @@
       </c>
       <c r="AG101" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -35606,7 +35741,7 @@
       </c>
       <c r="AA102" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB102" s="9" t="n">
@@ -35634,7 +35769,7 @@
       </c>
       <c r="AG102" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -35715,7 +35850,7 @@
       </c>
       <c r="AA103" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB103" s="9" t="n">
@@ -35743,7 +35878,7 @@
       </c>
       <c r="AG103" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -35824,7 +35959,7 @@
       </c>
       <c r="AA104" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB104" s="9" t="n">
@@ -35852,7 +35987,7 @@
       </c>
       <c r="AG104" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -35961,7 +36096,7 @@
       </c>
       <c r="AG105" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -36066,7 +36201,7 @@
       </c>
       <c r="AG106" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -36171,7 +36306,7 @@
       </c>
       <c r="AG107" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -36276,7 +36411,7 @@
       </c>
       <c r="AG108" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -36381,7 +36516,7 @@
       </c>
       <c r="AG109" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -36490,7 +36625,7 @@
       </c>
       <c r="AG110" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -36595,7 +36730,7 @@
       </c>
       <c r="AG111" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -36704,7 +36839,7 @@
       </c>
       <c r="AG112" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -36809,7 +36944,7 @@
       </c>
       <c r="AG113" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -36914,7 +37049,7 @@
       </c>
       <c r="AG114" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -37019,7 +37154,7 @@
       </c>
       <c r="AG115" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -37124,7 +37259,7 @@
       </c>
       <c r="AG116" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -37229,7 +37364,7 @@
       </c>
       <c r="AG117" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -37334,7 +37469,7 @@
       </c>
       <c r="AG118" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -37439,7 +37574,7 @@
       </c>
       <c r="AG119" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -37544,7 +37679,7 @@
       </c>
       <c r="AG120" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -37649,7 +37784,7 @@
       </c>
       <c r="AG121" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -37754,7 +37889,7 @@
       </c>
       <c r="AG122" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -37859,7 +37994,7 @@
       </c>
       <c r="AG123" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -37964,7 +38099,7 @@
       </c>
       <c r="AG124" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -38069,7 +38204,7 @@
       </c>
       <c r="AG125" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -38174,7 +38309,7 @@
       </c>
       <c r="AG126" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -38279,7 +38414,7 @@
       </c>
       <c r="AG127" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -38384,7 +38519,7 @@
       </c>
       <c r="AG128" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -38489,7 +38624,7 @@
       </c>
       <c r="AG129" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -38594,7 +38729,7 @@
       </c>
       <c r="AG130" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -38699,7 +38834,7 @@
       </c>
       <c r="AG131" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -38804,7 +38939,7 @@
       </c>
       <c r="AG132" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -38909,7 +39044,7 @@
       </c>
       <c r="AG133" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -39014,7 +39149,7 @@
       </c>
       <c r="AG134" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -39119,7 +39254,7 @@
       </c>
       <c r="AG135" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -39224,7 +39359,7 @@
       </c>
       <c r="AG136" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -39329,7 +39464,7 @@
       </c>
       <c r="AG137" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -39434,7 +39569,7 @@
       </c>
       <c r="AG138" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -39539,7 +39674,7 @@
       </c>
       <c r="AG139" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -39644,7 +39779,7 @@
       </c>
       <c r="AG140" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -39749,7 +39884,7 @@
       </c>
       <c r="AG141" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -39854,7 +39989,7 @@
       </c>
       <c r="AG142" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -39959,7 +40094,7 @@
       </c>
       <c r="AG143" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -40064,7 +40199,7 @@
       </c>
       <c r="AG144" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -40169,7 +40304,7 @@
       </c>
       <c r="AG145" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -40274,7 +40409,7 @@
       </c>
       <c r="AG146" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -40379,7 +40514,7 @@
       </c>
       <c r="AG147" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -40484,7 +40619,7 @@
       </c>
       <c r="AG148" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -40589,7 +40724,7 @@
       </c>
       <c r="AG149" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -40650,7 +40785,7 @@
       </c>
       <c r="AA150" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB150" s="9" t="n">
@@ -40678,7 +40813,7 @@
       </c>
       <c r="AG150" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -40739,7 +40874,7 @@
       </c>
       <c r="AA151" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB151" s="9" t="n">
@@ -40767,7 +40902,7 @@
       </c>
       <c r="AG151" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -40840,7 +40975,7 @@
       </c>
       <c r="AA152" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB152" s="9" t="n">
@@ -40868,7 +41003,7 @@
       </c>
       <c r="AG152" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -40941,7 +41076,7 @@
       </c>
       <c r="AA153" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB153" s="9" t="n">
@@ -40969,7 +41104,7 @@
       </c>
       <c r="AG153" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -41042,7 +41177,7 @@
       </c>
       <c r="AA154" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB154" s="9" t="n">
@@ -41070,7 +41205,7 @@
       </c>
       <c r="AG154" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -41143,7 +41278,7 @@
       </c>
       <c r="AA155" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB155" s="9" t="n">
@@ -41171,7 +41306,7 @@
       </c>
       <c r="AG155" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -41244,7 +41379,7 @@
       </c>
       <c r="AA156" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB156" s="9" t="n">
@@ -41272,7 +41407,7 @@
       </c>
       <c r="AG156" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -41345,7 +41480,7 @@
       </c>
       <c r="AA157" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB157" s="9" t="n">
@@ -41373,7 +41508,7 @@
       </c>
       <c r="AG157" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -41446,7 +41581,7 @@
       </c>
       <c r="AA158" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB158" s="9" t="n">
@@ -41474,7 +41609,7 @@
       </c>
       <c r="AG158" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -41547,7 +41682,7 @@
       </c>
       <c r="AA159" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB159" s="9" t="n">
@@ -41575,7 +41710,7 @@
       </c>
       <c r="AG159" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -41648,7 +41783,7 @@
       </c>
       <c r="AA160" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB160" s="9" t="n">
@@ -41676,7 +41811,7 @@
       </c>
       <c r="AG160" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -41749,7 +41884,7 @@
       </c>
       <c r="AA161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB161" s="9" t="n">
@@ -41777,7 +41912,7 @@
       </c>
       <c r="AG161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -41850,7 +41985,7 @@
       </c>
       <c r="AA162" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB162" s="9" t="n">
@@ -41878,7 +42013,7 @@
       </c>
       <c r="AG162" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -41951,7 +42086,7 @@
       </c>
       <c r="AA163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB163" s="9" t="n">
@@ -41979,7 +42114,7 @@
       </c>
       <c r="AG163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -42052,7 +42187,7 @@
       </c>
       <c r="AA164" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB164" s="9" t="n">
@@ -42080,7 +42215,7 @@
       </c>
       <c r="AG164" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -42153,7 +42288,7 @@
       </c>
       <c r="AA165" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB165" s="9" t="n">
@@ -42181,7 +42316,7 @@
       </c>
       <c r="AG165" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -42254,7 +42389,7 @@
       </c>
       <c r="AA166" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB166" s="9" t="n">
@@ -42282,7 +42417,7 @@
       </c>
       <c r="AG166" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -42355,7 +42490,7 @@
       </c>
       <c r="AA167" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB167" s="9" t="n">
@@ -42383,7 +42518,7 @@
       </c>
       <c r="AG167" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -42456,7 +42591,7 @@
       </c>
       <c r="AA168" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB168" s="9" t="n">
@@ -42484,7 +42619,7 @@
       </c>
       <c r="AG168" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -42557,7 +42692,7 @@
       </c>
       <c r="AA169" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB169" s="9" t="n">
@@ -42585,7 +42720,7 @@
       </c>
       <c r="AG169" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -42658,7 +42793,7 @@
       </c>
       <c r="AA170" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB170" s="9" t="n">
@@ -42686,7 +42821,7 @@
       </c>
       <c r="AG170" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -42759,7 +42894,7 @@
       </c>
       <c r="AA171" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB171" s="9" t="n">
@@ -42787,7 +42922,7 @@
       </c>
       <c r="AG171" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -42860,7 +42995,7 @@
       </c>
       <c r="AA172" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB172" s="9" t="n">
@@ -42888,7 +43023,7 @@
       </c>
       <c r="AG172" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -42961,7 +43096,7 @@
       </c>
       <c r="AA173" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB173" s="9" t="n">
@@ -42989,7 +43124,7 @@
       </c>
       <c r="AG173" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -43062,7 +43197,7 @@
       </c>
       <c r="AA174" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB174" s="9" t="n">
@@ -43090,7 +43225,7 @@
       </c>
       <c r="AG174" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -43163,7 +43298,7 @@
       </c>
       <c r="AA175" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB175" s="9" t="n">
@@ -43191,7 +43326,7 @@
       </c>
       <c r="AG175" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -43879,7 +44014,7 @@
       </c>
       <c r="AG2" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -44018,7 +44153,7 @@
       </c>
       <c r="AG3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -44153,7 +44288,7 @@
       </c>
       <c r="AG4" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -44278,7 +44413,7 @@
       </c>
       <c r="AG5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -44399,7 +44534,7 @@
       </c>
       <c r="AG6" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -44516,7 +44651,7 @@
       </c>
       <c r="AG7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -44641,7 +44776,7 @@
       </c>
       <c r="AG8" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -44758,7 +44893,7 @@
       </c>
       <c r="AG9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -44879,7 +45014,7 @@
       </c>
       <c r="AG10" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -44996,7 +45131,7 @@
       </c>
       <c r="AG11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -45101,7 +45236,7 @@
       </c>
       <c r="AG12" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -45206,7 +45341,7 @@
       </c>
       <c r="AG13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -45311,7 +45446,7 @@
       </c>
       <c r="AG14" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -45416,7 +45551,7 @@
       </c>
       <c r="AG15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -45521,7 +45656,7 @@
       </c>
       <c r="AG16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -45626,7 +45761,7 @@
       </c>
       <c r="AG17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -45731,7 +45866,7 @@
       </c>
       <c r="AG18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -45836,7 +45971,7 @@
       </c>
       <c r="AG19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -45941,7 +46076,7 @@
       </c>
       <c r="AG20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -46026,7 +46161,7 @@
       </c>
       <c r="AA21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB21" s="9" t="n">
@@ -46050,7 +46185,7 @@
       </c>
       <c r="AG21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -46131,7 +46266,7 @@
       </c>
       <c r="AA22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB22" s="9" t="n">
@@ -46155,7 +46290,7 @@
       </c>
       <c r="AG22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -46240,7 +46375,7 @@
       </c>
       <c r="AA23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB23" s="9" t="n">
@@ -46264,7 +46399,7 @@
       </c>
       <c r="AG23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -46345,7 +46480,7 @@
       </c>
       <c r="AA24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB24" s="9" t="n">
@@ -46369,7 +46504,7 @@
       </c>
       <c r="AG24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -46450,7 +46585,7 @@
       </c>
       <c r="AA25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB25" s="9" t="n">
@@ -46474,7 +46609,7 @@
       </c>
       <c r="AG25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -46555,7 +46690,7 @@
       </c>
       <c r="AA26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB26" s="9" t="n">
@@ -46579,7 +46714,7 @@
       </c>
       <c r="AG26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -46660,7 +46795,7 @@
       </c>
       <c r="AA27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB27" s="9" t="n">
@@ -46684,7 +46819,7 @@
       </c>
       <c r="AG27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -46765,7 +46900,7 @@
       </c>
       <c r="AA28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB28" s="9" t="n">
@@ -46789,7 +46924,7 @@
       </c>
       <c r="AG28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -46870,7 +47005,7 @@
       </c>
       <c r="AA29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB29" s="9" t="n">
@@ -46894,7 +47029,7 @@
       </c>
       <c r="AG29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -46975,7 +47110,7 @@
       </c>
       <c r="AA30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB30" s="9" t="n">
@@ -46999,7 +47134,7 @@
       </c>
       <c r="AG30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -47080,7 +47215,7 @@
       </c>
       <c r="AA31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB31" s="9" t="n">
@@ -47104,7 +47239,7 @@
       </c>
       <c r="AG31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -47177,7 +47312,7 @@
       </c>
       <c r="AA32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB32" s="9" t="n">
@@ -47205,7 +47340,7 @@
       </c>
       <c r="AG32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -47638,7 +47773,7 @@
       </c>
       <c r="AG2" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -47773,7 +47908,7 @@
       </c>
       <c r="AG3" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -47864,7 +47999,7 @@
       </c>
       <c r="AA4" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB4" s="9" t="n">
@@ -47892,7 +48027,7 @@
       </c>
       <c r="AG4" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -47983,7 +48118,7 @@
       </c>
       <c r="AA5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB5" s="9" t="n">
@@ -48011,7 +48146,7 @@
       </c>
       <c r="AG5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -48102,7 +48237,7 @@
       </c>
       <c r="AA6" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB6" s="9" t="n">
@@ -48130,7 +48265,7 @@
       </c>
       <c r="AG6" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -48221,7 +48356,7 @@
       </c>
       <c r="AA7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB7" s="9" t="n">
@@ -48249,7 +48384,7 @@
       </c>
       <c r="AG7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -48340,7 +48475,7 @@
       </c>
       <c r="AA8" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB8" s="9" t="n">
@@ -48368,7 +48503,7 @@
       </c>
       <c r="AG8" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -48459,7 +48594,7 @@
       </c>
       <c r="AA9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB9" s="9" t="n">
@@ -48487,7 +48622,7 @@
       </c>
       <c r="AG9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -48578,7 +48713,7 @@
       </c>
       <c r="AA10" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB10" s="9" t="n">
@@ -48606,7 +48741,7 @@
       </c>
       <c r="AG10" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -48697,7 +48832,7 @@
       </c>
       <c r="AA11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB11" s="9" t="n">
@@ -48725,7 +48860,7 @@
       </c>
       <c r="AG11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -48816,7 +48951,7 @@
       </c>
       <c r="AA12" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB12" s="9" t="n">
@@ -48844,7 +48979,7 @@
       </c>
       <c r="AG12" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -48935,7 +49070,7 @@
       </c>
       <c r="AA13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB13" s="9" t="n">
@@ -48963,7 +49098,7 @@
       </c>
       <c r="AG13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -49054,7 +49189,7 @@
       </c>
       <c r="AA14" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB14" s="9" t="n">
@@ -49082,7 +49217,7 @@
       </c>
       <c r="AG14" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -49173,7 +49308,7 @@
       </c>
       <c r="AA15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB15" s="9" t="n">
@@ -49201,7 +49336,7 @@
       </c>
       <c r="AG15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -49292,7 +49427,7 @@
       </c>
       <c r="AA16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB16" s="9" t="n">
@@ -49320,7 +49455,7 @@
       </c>
       <c r="AG16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -49411,7 +49546,7 @@
       </c>
       <c r="AA17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB17" s="9" t="n">
@@ -49439,7 +49574,7 @@
       </c>
       <c r="AG17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -49530,7 +49665,7 @@
       </c>
       <c r="AA18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB18" s="9" t="n">
@@ -49558,7 +49693,7 @@
       </c>
       <c r="AG18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -49649,7 +49784,7 @@
       </c>
       <c r="AA19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB19" s="9" t="n">
@@ -49677,7 +49812,7 @@
       </c>
       <c r="AG19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -49768,7 +49903,7 @@
       </c>
       <c r="AA20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB20" s="9" t="n">
@@ -49796,7 +49931,7 @@
       </c>
       <c r="AG20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -49887,7 +50022,7 @@
       </c>
       <c r="AA21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB21" s="9" t="n">
@@ -49915,7 +50050,7 @@
       </c>
       <c r="AG21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -50006,7 +50141,7 @@
       </c>
       <c r="AA22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB22" s="9" t="n">
@@ -50034,7 +50169,7 @@
       </c>
       <c r="AG22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -50125,7 +50260,7 @@
       </c>
       <c r="AA23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB23" s="9" t="n">
@@ -50153,7 +50288,7 @@
       </c>
       <c r="AG23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -50244,7 +50379,7 @@
       </c>
       <c r="AA24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB24" s="9" t="n">
@@ -50272,7 +50407,7 @@
       </c>
       <c r="AG24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -50363,7 +50498,7 @@
       </c>
       <c r="AA25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB25" s="9" t="n">
@@ -50391,7 +50526,7 @@
       </c>
       <c r="AG25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -50482,7 +50617,7 @@
       </c>
       <c r="AA26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB26" s="9" t="n">
@@ -50510,7 +50645,7 @@
       </c>
       <c r="AG26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -50601,7 +50736,7 @@
       </c>
       <c r="AA27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB27" s="9" t="n">
@@ -50629,7 +50764,7 @@
       </c>
       <c r="AG27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -50720,7 +50855,7 @@
       </c>
       <c r="AA28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB28" s="9" t="n">
@@ -50748,7 +50883,7 @@
       </c>
       <c r="AG28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -50839,7 +50974,7 @@
       </c>
       <c r="AA29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB29" s="9" t="n">
@@ -50867,7 +51002,7 @@
       </c>
       <c r="AG29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -50958,7 +51093,7 @@
       </c>
       <c r="AA30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB30" s="9" t="n">
@@ -50986,7 +51121,7 @@
       </c>
       <c r="AG30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -51077,7 +51212,7 @@
       </c>
       <c r="AA31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB31" s="9" t="n">
@@ -51105,7 +51240,7 @@
       </c>
       <c r="AG31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -51196,7 +51331,7 @@
       </c>
       <c r="AA32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB32" s="9" t="n">
@@ -51224,7 +51359,7 @@
       </c>
       <c r="AG32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -51315,7 +51450,7 @@
       </c>
       <c r="AA33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB33" s="9" t="n">
@@ -51343,7 +51478,7 @@
       </c>
       <c r="AG33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -51434,7 +51569,7 @@
       </c>
       <c r="AA34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB34" s="9" t="n">
@@ -51462,7 +51597,7 @@
       </c>
       <c r="AG34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -51553,7 +51688,7 @@
       </c>
       <c r="AA35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB35" s="9" t="n">
@@ -51581,7 +51716,7 @@
       </c>
       <c r="AG35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -51672,7 +51807,7 @@
       </c>
       <c r="AA36" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB36" s="9" t="n">
@@ -51700,7 +51835,7 @@
       </c>
       <c r="AG36" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -51791,7 +51926,7 @@
       </c>
       <c r="AA37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB37" s="9" t="n">
@@ -51819,7 +51954,7 @@
       </c>
       <c r="AG37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -51910,7 +52045,7 @@
       </c>
       <c r="AA38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB38" s="9" t="n">
@@ -51938,7 +52073,7 @@
       </c>
       <c r="AG38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -52029,7 +52164,7 @@
       </c>
       <c r="AA39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB39" s="9" t="n">
@@ -52057,7 +52192,7 @@
       </c>
       <c r="AG39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -52148,7 +52283,7 @@
       </c>
       <c r="AA40" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB40" s="9" t="n">
@@ -52176,7 +52311,7 @@
       </c>
       <c r="AG40" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -52267,7 +52402,7 @@
       </c>
       <c r="AA41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB41" s="9" t="n">
@@ -52295,7 +52430,7 @@
       </c>
       <c r="AG41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -52386,7 +52521,7 @@
       </c>
       <c r="AA42" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB42" s="9" t="n">
@@ -52414,7 +52549,7 @@
       </c>
       <c r="AG42" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -52505,7 +52640,7 @@
       </c>
       <c r="AA43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB43" s="9" t="n">
@@ -52533,7 +52668,7 @@
       </c>
       <c r="AG43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -52624,7 +52759,7 @@
       </c>
       <c r="AA44" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB44" s="9" t="n">
@@ -52652,7 +52787,7 @@
       </c>
       <c r="AG44" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -52743,7 +52878,7 @@
       </c>
       <c r="AA45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB45" s="9" t="n">
@@ -52771,7 +52906,7 @@
       </c>
       <c r="AG45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -52858,7 +52993,7 @@
       </c>
       <c r="AA46" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB46" s="9" t="n">
@@ -52886,7 +53021,7 @@
       </c>
       <c r="AG46" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -52977,7 +53112,7 @@
       </c>
       <c r="AA47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB47" s="9" t="n">
@@ -53005,7 +53140,7 @@
       </c>
       <c r="AG47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -53096,7 +53231,7 @@
       </c>
       <c r="AA48" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB48" s="9" t="n">
@@ -53124,7 +53259,7 @@
       </c>
       <c r="AG48" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -53215,7 +53350,7 @@
       </c>
       <c r="AA49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB49" s="9" t="n">
@@ -53243,7 +53378,7 @@
       </c>
       <c r="AG49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -53334,7 +53469,7 @@
       </c>
       <c r="AA50" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB50" s="9" t="n">
@@ -53362,7 +53497,7 @@
       </c>
       <c r="AG50" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -53453,7 +53588,7 @@
       </c>
       <c r="AA51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB51" s="9" t="n">
@@ -53481,7 +53616,7 @@
       </c>
       <c r="AG51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -53568,7 +53703,7 @@
       </c>
       <c r="AA52" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB52" s="9" t="n">
@@ -53596,7 +53731,7 @@
       </c>
       <c r="AG52" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -53683,7 +53818,7 @@
       </c>
       <c r="AA53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB53" s="9" t="n">
@@ -53711,7 +53846,7 @@
       </c>
       <c r="AG53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -53802,7 +53937,7 @@
       </c>
       <c r="AA54" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB54" s="9" t="n">
@@ -53830,7 +53965,7 @@
       </c>
       <c r="AG54" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -53917,7 +54052,7 @@
       </c>
       <c r="AA55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB55" s="9" t="n">
@@ -53945,7 +54080,7 @@
       </c>
       <c r="AG55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -54371,7 +54506,7 @@
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB2" s="5" t="n">
@@ -54395,7 +54530,7 @@
       </c>
       <c r="AG2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -54486,7 +54621,7 @@
       </c>
       <c r="AA3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB3" s="7" t="n">
@@ -54514,7 +54649,7 @@
       </c>
       <c r="AG3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -54621,7 +54756,7 @@
       </c>
       <c r="AA4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB4" s="7" t="n">
@@ -54645,7 +54780,7 @@
       </c>
       <c r="AG4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -54788,7 +54923,7 @@
       </c>
       <c r="AG5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -54923,7 +55058,7 @@
       </c>
       <c r="AG6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -55062,7 +55197,7 @@
       </c>
       <c r="AG7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -55193,7 +55328,7 @@
       </c>
       <c r="AG8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -55320,7 +55455,7 @@
       </c>
       <c r="AG9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -55467,7 +55602,7 @@
       </c>
       <c r="AG10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -55594,7 +55729,7 @@
       </c>
       <c r="AG11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -55697,7 +55832,7 @@
       </c>
       <c r="AA12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB12" s="7" t="n">
@@ -55721,7 +55856,7 @@
       </c>
       <c r="AG12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -55860,7 +55995,7 @@
       </c>
       <c r="AG13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -55991,7 +56126,7 @@
       </c>
       <c r="AG14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -56130,7 +56265,7 @@
       </c>
       <c r="AG15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -56477,7 +56612,7 @@
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB2" s="5" t="n">
@@ -56501,7 +56636,7 @@
       </c>
       <c r="AG2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -56592,7 +56727,7 @@
       </c>
       <c r="AA3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB3" s="7" t="n">
@@ -56620,7 +56755,7 @@
       </c>
       <c r="AG3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -56727,7 +56862,7 @@
       </c>
       <c r="AA4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB4" s="7" t="n">
@@ -56751,7 +56886,7 @@
       </c>
       <c r="AG4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -56894,7 +57029,7 @@
       </c>
       <c r="AG5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -57029,7 +57164,7 @@
       </c>
       <c r="AG6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -57168,7 +57303,7 @@
       </c>
       <c r="AG7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -57299,7 +57434,7 @@
       </c>
       <c r="AG8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -57426,7 +57561,7 @@
       </c>
       <c r="AG9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -57573,7 +57708,7 @@
       </c>
       <c r="AG10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -57700,7 +57835,7 @@
       </c>
       <c r="AG11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -57803,7 +57938,7 @@
       </c>
       <c r="AA12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:16</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
       <c r="AB12" s="7" t="n">
@@ -57827,7 +57962,7 @@
       </c>
       <c r="AG12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -57966,7 +58101,7 @@
       </c>
       <c r="AG13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -58097,7 +58232,7 @@
       </c>
       <c r="AG14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
@@ -58236,7 +58371,7 @@
       </c>
       <c r="AG15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09T21:15:17</t>
+          <t>2026-07-09T20:07:45</t>
         </is>
       </c>
     </row>
